--- a/www/flightdata/xlsx/eoss-347.xlsx
+++ b/www/flightdata/xlsx/eoss-347.xlsx
@@ -3087,7 +3087,7 @@
         <v>26498.4</v>
       </c>
       <c r="I2">
-        <v>528</v>
+        <v>378</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
